--- a/03-成熟度评估/03-局部评估/03-热处理工序成熟度评估表.xlsx
+++ b/03-成熟度评估/03-局部评估/03-热处理工序成熟度评估表.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,11 +122,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -150,6 +159,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -533,7 +543,13 @@
           <t>03-热处理工序成熟度评估表</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -541,6 +557,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -548,13 +565,15 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>热处理是紧固件制造的关键性能保障工序，通过淬火、回火等工艺提高产品的硬度、强度和耐磨性。该工序的工艺控制精度直接影响产品的力学性能和使用寿命。热处理工序需符合CQI-9（热处理系统评审）要求。</t>
-        </is>
-      </c>
-    </row>
+          <t>热处理是制造的关键性能保障工序，通过淬火、回火等工艺提高产品的硬度、强度和耐磨性。该工序的工艺控制精度直接影响产品的力学性能和使用寿命。热处理工序需符合CQI-9（热处理系统评审）要求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -562,10 +581,11 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  网带炉/井式炉/箱式炉</t>
+          <t xml:space="preserve">  *  热处理炉/井式炉/箱式炉</t>
         </is>
       </c>
     </row>
@@ -597,6 +617,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
@@ -604,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -639,6 +661,9 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -646,6 +671,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
@@ -653,6 +679,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
@@ -660,6 +687,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
@@ -667,6 +695,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
@@ -674,6 +703,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
@@ -681,6 +711,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
@@ -688,6 +719,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
@@ -695,6 +727,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
@@ -702,6 +735,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -709,6 +743,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
@@ -716,6 +751,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
@@ -723,6 +759,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
@@ -730,6 +767,9 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
@@ -737,6 +777,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
@@ -744,6 +785,9 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
@@ -751,6 +795,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
@@ -758,6 +803,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
@@ -765,6 +811,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
@@ -772,6 +819,7 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
